--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Usme.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Usme.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F09FB0F3-4E3A-463A-8D40-25C42B6B69F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318E0CA4-3275-114E-9261-1E843E4CD4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6C8C3A43-1AC2-4AF8-8538-8019854A03E5}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{6C8C3A43-1AC2-4AF8-8538-8019854A03E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,11 +219,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -315,10 +325,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -329,12 +340,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -649,9 +666,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDBB8AD-3155-46C3-9CEA-E82BD1F12339}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:V5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="56" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -719,251 +736,254 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="5">
-        <v>5</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="M2" s="4">
+        <v>3</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="5">
-        <v>5</v>
-      </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="4">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="5">
-        <v>5</v>
-      </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="4">
+        <v>3</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="5">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="S2" s="4">
+        <v>3</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="5">
-        <v>5</v>
-      </c>
-      <c r="V2" s="5"/>
+      <c r="U2" s="4">
+        <v>3</v>
+      </c>
+      <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="5">
-        <v>5</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="M3" s="4">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="5">
-        <v>5</v>
-      </c>
-      <c r="P3" s="5" t="s">
+      <c r="O3" s="4">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="5">
-        <v>5</v>
-      </c>
-      <c r="R3" s="5" t="s">
+      <c r="Q3" s="4">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="5">
-        <v>5</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="S3" s="4">
+        <v>3</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="5">
-        <v>5</v>
-      </c>
-      <c r="V3" s="5"/>
+      <c r="U3" s="4">
+        <v>3</v>
+      </c>
+      <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="5">
-        <v>5</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="M4" s="4">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="5">
-        <v>5</v>
-      </c>
-      <c r="P4" s="5" t="s">
+      <c r="O4" s="4">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="5">
-        <v>5</v>
-      </c>
-      <c r="R4" s="5" t="s">
+      <c r="Q4" s="4">
+        <v>3</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="5">
-        <v>5</v>
-      </c>
-      <c r="T4" s="5" t="s">
+      <c r="S4" s="4">
+        <v>3</v>
+      </c>
+      <c r="T4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="5">
-        <v>5</v>
-      </c>
-      <c r="V4" s="5"/>
+      <c r="U4" s="4">
+        <v>3</v>
+      </c>
+      <c r="V4" s="4"/>
     </row>
-    <row r="5" spans="1:22" ht="50" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:22" ht="224" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="5">
-        <v>5</v>
-      </c>
-      <c r="N5" s="5" t="s">
+      <c r="M5" s="4">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="5">
-        <v>5</v>
-      </c>
-      <c r="P5" s="5" t="s">
+      <c r="O5" s="4">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="Q5" s="5">
-        <v>5</v>
-      </c>
-      <c r="R5" s="5" t="s">
+      <c r="Q5" s="4">
+        <v>1</v>
+      </c>
+      <c r="R5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S5" s="5">
-        <v>5</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U5" s="5">
-        <v>5</v>
-      </c>
-      <c r="V5" s="5"/>
+      <c r="U5" s="4">
+        <v>1</v>
+      </c>
+      <c r="V5" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{59AAAB02-1A3A-2A49-9292-4A3293C6786D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Usme.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p28/Alcaldía Local De Usme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p28/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318E0CA4-3275-114E-9261-1E843E4CD4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F918F6E-BE26-EE4C-A98E-7C74FC0C1E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16680" xr2:uid="{6C8C3A43-1AC2-4AF8-8538-8019854A03E5}"/>
   </bookViews>
